--- a/artfynd/A 7506-2023 artfynd.xlsx
+++ b/artfynd/A 7506-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7506-2023 artfynd.xlsx
+++ b/artfynd/A 7506-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102625801</v>
+        <v>96406389</v>
       </c>
       <c r="B2" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>220204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,17 +710,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedtorp 250m N, Srm</t>
+          <t>Överhändö 400m o, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600563.1137439634</v>
+        <v>600481</v>
       </c>
       <c r="R2" t="n">
-        <v>6562333.343980189</v>
+        <v>6562403</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,6 +779,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102625801</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hedtorp 250m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>600563</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6562334</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägdike</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7506-2023 artfynd.xlsx
+++ b/artfynd/A 7506-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96406389</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,8 +896,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102625801</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>